--- a/DataDictionary_Template.xlsx
+++ b/DataDictionary_Template.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F7D36F-1E64-4BDB-ABDD-A2A1B44AE4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275E56FF-9F52-430C-8116-3391968BD6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9345" yWindow="3585" windowWidth="14415" windowHeight="10590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataDictionary" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="116">
   <si>
     <t>Data Dictionary</t>
   </si>
@@ -153,9 +153,6 @@
     <t>customer_id</t>
   </si>
   <si>
-    <t>loyalty_points</t>
-  </si>
-  <si>
     <t>registration_date</t>
   </si>
   <si>
@@ -183,12 +180,6 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>last_login</t>
-  </si>
-  <si>
-    <t>created_by</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -213,9 +204,6 @@
     <t>total_amount</t>
   </si>
   <si>
-    <t>payment_method</t>
-  </si>
-  <si>
     <t>DECIMAL</t>
   </si>
   <si>
@@ -234,9 +222,6 @@
     <t>unit_price_at_time</t>
   </si>
   <si>
-    <t>discount</t>
-  </si>
-  <si>
     <t>Table inventory_transactions</t>
   </si>
   <si>
@@ -337,6 +322,48 @@
   </si>
   <si>
     <t>номер сотрудника</t>
+  </si>
+  <si>
+    <t>цена за еденицу товаров</t>
+  </si>
+  <si>
+    <t>количество товара запасом</t>
+  </si>
+  <si>
+    <t>уровень повторного заказа</t>
+  </si>
+  <si>
+    <t>идентификатор клиентов</t>
+  </si>
+  <si>
+    <t>имя клиента</t>
+  </si>
+  <si>
+    <t>почта</t>
+  </si>
+  <si>
+    <t>фамилия клиента</t>
+  </si>
+  <si>
+    <t>дата регистрации</t>
+  </si>
+  <si>
+    <t>пароль</t>
+  </si>
+  <si>
+    <t>активность</t>
+  </si>
+  <si>
+    <t>общая сумма</t>
+  </si>
+  <si>
+    <t>заказ товаров</t>
+  </si>
+  <si>
+    <t>количество</t>
+  </si>
+  <si>
+    <t>цена в еденицу</t>
   </si>
 </sst>
 </file>
@@ -442,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -489,23 +516,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -852,31 +870,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" ht="18.75">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="30">
       <c r="A5" s="4" t="s">
@@ -909,7 +927,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -924,7 +942,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -955,13 +973,13 @@
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" ht="30">
       <c r="A15" s="4" t="s">
@@ -994,7 +1012,7 @@
         <v>7</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1009,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1024,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1039,7 +1057,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="21.75" customHeight="1">
@@ -1054,7 +1072,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.25" customHeight="1">
@@ -1070,13 +1088,13 @@
       <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="25" spans="1:5" ht="30">
       <c r="A25" s="4" t="s">
@@ -1109,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="20.25" customHeight="1">
@@ -1124,7 +1142,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1139,7 +1157,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1156,7 +1174,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1173,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1187,6 +1205,9 @@
       <c r="D31" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="E31" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6"/>
@@ -1199,7 +1220,9 @@
       <c r="D32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6"/>
@@ -1212,6 +1235,9 @@
       <c r="D33" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="E33" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="21.75" customHeight="1">
       <c r="A34" s="6"/>
@@ -1227,24 +1253,24 @@
       <c r="E34" s="1"/>
     </row>
     <row r="35" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A35" s="19"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="21"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="8"/>
     </row>
     <row r="36" spans="1:5" ht="20.25" customHeight="1">
       <c r="A36" s="3"/>
       <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:5" ht="30">
       <c r="A38" s="4" t="s">
@@ -1277,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1292,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1307,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1322,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1337,7 +1363,7 @@
         <v>7</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1352,7 +1378,7 @@
         <v>7</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1367,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1375,13 +1401,13 @@
       <c r="D46" s="3"/>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
     </row>
     <row r="48" spans="1:5" ht="30">
       <c r="A48" s="4" t="s">
@@ -1414,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1428,7 +1454,9 @@
       <c r="D50" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6"/>
@@ -1441,7 +1469,9 @@
       <c r="D51" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6"/>
@@ -1454,6 +1484,9 @@
       <c r="D52" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="E52" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6"/>
@@ -1466,7 +1499,9 @@
       <c r="D53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="15"/>
+      <c r="E53" s="15" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6"/>
@@ -1474,37 +1509,31 @@
         <v>45</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="E54" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="6"/>
-      <c r="B55" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="1"/>
+      <c r="A55" s="3"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3"/>
       <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
+      <c r="A57" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
     </row>
     <row r="58" spans="1:5" ht="30">
       <c r="A58" s="4" t="s">
@@ -1528,7 +1557,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>12</v>
@@ -1537,13 +1566,13 @@
         <v>7</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6"/>
       <c r="B60" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>8</v>
@@ -1552,26 +1581,28 @@
         <v>7</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6"/>
       <c r="B61" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="D61" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="1"/>
+      <c r="E61" s="1" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6"/>
       <c r="B62" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>31</v>
@@ -1580,7 +1611,7 @@
         <v>7</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1595,7 +1626,7 @@
         <v>7</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1610,22 +1641,22 @@
         <v>7</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6"/>
       <c r="B65" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1639,66 +1670,42 @@
       <c r="D66" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E66" s="1"/>
+      <c r="E66" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6"/>
       <c r="B67" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="6"/>
-      <c r="B68" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="15"/>
+      <c r="A68" s="3"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="6"/>
-      <c r="B69" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="3"/>
+      <c r="D70" s="3"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="1"/>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
     </row>
     <row r="73" spans="1:5" ht="30">
       <c r="A73" s="4" t="s">
@@ -1722,7 +1729,7 @@
         <v>6</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>12</v>
@@ -1731,7 +1738,7 @@
         <v>7</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1748,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1765,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1773,7 +1780,7 @@
         <v>34</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>12</v>
@@ -1782,40 +1789,43 @@
         <v>7</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6"/>
       <c r="B78" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6"/>
       <c r="B79" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>7</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6"/>
       <c r="B80" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>10</v>
@@ -1823,31 +1833,22 @@
       <c r="D80" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="1"/>
+      <c r="E80" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="A81" s="3"/>
+      <c r="D81" s="3"/>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B83" s="18"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="A83" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
     </row>
     <row r="84" spans="1:5" ht="30">
       <c r="A84" s="4" t="s">
@@ -1871,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>12</v>
@@ -1879,14 +1880,16 @@
       <c r="D85" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E85" s="1"/>
+      <c r="E85" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>12</v>
@@ -1895,7 +1898,7 @@
         <v>7</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1912,58 +1915,55 @@
         <v>7</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6"/>
       <c r="B88" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>7</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6"/>
       <c r="B89" s="14" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E89" s="15"/>
+      <c r="E89" s="15" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="6"/>
-      <c r="B90" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>7</v>
-      </c>
+      <c r="A90" s="3"/>
+      <c r="D90" s="3"/>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="3"/>
       <c r="D91" s="3"/>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
+      <c r="A92" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
     </row>
     <row r="93" spans="1:5" ht="30">
       <c r="A93" s="4" t="s">
@@ -1987,7 +1987,7 @@
         <v>6</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>12</v>
@@ -1996,7 +1996,7 @@
         <v>7</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2013,7 +2013,7 @@
         <v>7</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2021,7 +2021,7 @@
         <v>34</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>12</v>
@@ -2034,7 +2034,7 @@
     <row r="97" spans="1:5">
       <c r="A97" s="6"/>
       <c r="B97" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     <row r="98" spans="1:5">
       <c r="A98" s="6"/>
       <c r="B98" s="14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D98" s="13" t="s">
         <v>7</v>
@@ -2059,10 +2059,10 @@
     <row r="99" spans="1:5">
       <c r="A99" s="6"/>
       <c r="B99" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>7</v>
@@ -2102,17 +2102,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A72:E72"/>
     <mergeCell ref="A83:E83"/>
     <mergeCell ref="A92:E92"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.2" right="0.2" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
